--- a/artfynd/A 22939-2020 artfynd.xlsx
+++ b/artfynd/A 22939-2020 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>118642567</v>
       </c>
       <c r="B3" t="n">
-        <v>102956</v>
+        <v>102963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
